--- a/output/yearly_total_coral_cover_iteration_61_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_61_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.288864338847421</v>
+        <v>1.25067435315222</v>
       </c>
       <c r="C3" t="n">
-        <v>4.647080068915241</v>
+        <v>4.646049233825782</v>
       </c>
       <c r="D3" t="n">
-        <v>6.183130583835912</v>
+        <v>6.101144833054261</v>
       </c>
       <c r="E3" t="n">
-        <v>12.11907499159857</v>
+        <v>11.99786842003226</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.464155833353559</v>
+        <v>1.370616014667294</v>
       </c>
       <c r="C4" t="n">
-        <v>5.166230893053422</v>
+        <v>5.170187911114808</v>
       </c>
       <c r="D4" t="n">
-        <v>6.442859281549647</v>
+        <v>6.502601069062296</v>
       </c>
       <c r="E4" t="n">
-        <v>13.07324600795663</v>
+        <v>13.0434049948444</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.682138694577871</v>
+        <v>1.534896116959291</v>
       </c>
       <c r="C5" t="n">
-        <v>5.861534221150902</v>
+        <v>5.825039757796503</v>
       </c>
       <c r="D5" t="n">
-        <v>6.73591565771485</v>
+        <v>6.832103668825276</v>
       </c>
       <c r="E5" t="n">
-        <v>14.27958857344362</v>
+        <v>14.19203954358107</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.921000856646464</v>
+        <v>1.724327004521076</v>
       </c>
       <c r="C6" t="n">
-        <v>6.742108150839133</v>
+        <v>6.626549496655651</v>
       </c>
       <c r="D6" t="n">
-        <v>7.020145365416919</v>
+        <v>7.352057000004535</v>
       </c>
       <c r="E6" t="n">
-        <v>15.68325437290252</v>
+        <v>15.70293350118126</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.183951603921263</v>
+        <v>1.933084855301881</v>
       </c>
       <c r="C7" t="n">
-        <v>7.78933974811948</v>
+        <v>7.570774390771291</v>
       </c>
       <c r="D7" t="n">
-        <v>7.424946380062244</v>
+        <v>7.764617743177852</v>
       </c>
       <c r="E7" t="n">
-        <v>17.39823773210299</v>
+        <v>17.26847698925102</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.339773463031687</v>
+        <v>1.161418265847751</v>
       </c>
       <c r="C8" t="n">
-        <v>5.465470862209544</v>
+        <v>5.219426062044588</v>
       </c>
       <c r="D8" t="n">
-        <v>5.648679338121076</v>
+        <v>5.992760363974981</v>
       </c>
       <c r="E8" t="n">
-        <v>12.45392366336231</v>
+        <v>12.37360469186732</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.657309147083643</v>
+        <v>1.449656636749821</v>
       </c>
       <c r="C9" t="n">
-        <v>6.728279345449641</v>
+        <v>6.389186370458434</v>
       </c>
       <c r="D9" t="n">
-        <v>6.130526902981356</v>
+        <v>6.515556245053477</v>
       </c>
       <c r="E9" t="n">
-        <v>14.51611539551464</v>
+        <v>14.35439925226173</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.988162315151048</v>
+        <v>1.748087354983464</v>
       </c>
       <c r="C10" t="n">
-        <v>8.154356601010232</v>
+        <v>7.693089312368494</v>
       </c>
       <c r="D10" t="n">
-        <v>6.619538026625078</v>
+        <v>7.085539493977075</v>
       </c>
       <c r="E10" t="n">
-        <v>16.76205694278636</v>
+        <v>16.52671616132903</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.315226592925721</v>
+        <v>2.056822697350973</v>
       </c>
       <c r="C11" t="n">
-        <v>9.669750142600767</v>
+        <v>9.105670047672584</v>
       </c>
       <c r="D11" t="n">
-        <v>7.140948528288662</v>
+        <v>7.755072904863267</v>
       </c>
       <c r="E11" t="n">
-        <v>19.12592526381515</v>
+        <v>18.91756564988682</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.636894067492483</v>
+        <v>2.355956558952342</v>
       </c>
       <c r="C12" t="n">
-        <v>11.22821276835168</v>
+        <v>10.59269388132084</v>
       </c>
       <c r="D12" t="n">
-        <v>7.658880652178032</v>
+        <v>8.348205553743034</v>
       </c>
       <c r="E12" t="n">
-        <v>21.5239874880222</v>
+        <v>21.29685599401622</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.955824530135402</v>
+        <v>2.647465084340884</v>
       </c>
       <c r="C13" t="n">
-        <v>12.82943575490384</v>
+        <v>12.14280747161502</v>
       </c>
       <c r="D13" t="n">
-        <v>8.111160438377226</v>
+        <v>9.007795093064074</v>
       </c>
       <c r="E13" t="n">
-        <v>23.89642072341647</v>
+        <v>23.79806764901998</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.722456712146944</v>
+        <v>1.526971109277319</v>
       </c>
       <c r="C14" t="n">
-        <v>8.976639586211839</v>
+        <v>8.56455098735424</v>
       </c>
       <c r="D14" t="n">
-        <v>6.158788055574473</v>
+        <v>6.810933603074502</v>
       </c>
       <c r="E14" t="n">
-        <v>16.85788435393325</v>
+        <v>16.90245569970606</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.753990448407351</v>
+        <v>1.552977605962817</v>
       </c>
       <c r="C15" t="n">
-        <v>9.643913865834312</v>
+        <v>9.232316140828836</v>
       </c>
       <c r="D15" t="n">
-        <v>6.16486507386376</v>
+        <v>6.911994711749669</v>
       </c>
       <c r="E15" t="n">
-        <v>17.56276938810542</v>
+        <v>17.69728845854132</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.025237521613703</v>
+        <v>1.786447027509751</v>
       </c>
       <c r="C16" t="n">
-        <v>11.3068079447646</v>
+        <v>10.87238458563539</v>
       </c>
       <c r="D16" t="n">
-        <v>6.693536212600669</v>
+        <v>7.536356799219512</v>
       </c>
       <c r="E16" t="n">
-        <v>20.02558167897897</v>
+        <v>20.19518841236465</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.612991843123424</v>
+        <v>1.422306986527567</v>
       </c>
       <c r="C17" t="n">
-        <v>10.31505623141152</v>
+        <v>9.990902774423304</v>
       </c>
       <c r="D17" t="n">
-        <v>6.222366036901496</v>
+        <v>7.077448652346384</v>
       </c>
       <c r="E17" t="n">
-        <v>18.15041411143644</v>
+        <v>18.49065841329725</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.832167018096525</v>
+        <v>1.614346654955285</v>
       </c>
       <c r="C18" t="n">
-        <v>11.95940509620858</v>
+        <v>11.62786889648444</v>
       </c>
       <c r="D18" t="n">
-        <v>6.648238373526722</v>
+        <v>7.597009172387881</v>
       </c>
       <c r="E18" t="n">
-        <v>20.43981048783183</v>
+        <v>20.8392247238276</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.833914529010084</v>
+        <v>1.611931555602838</v>
       </c>
       <c r="C19" t="n">
-        <v>12.7366351187067</v>
+        <v>12.40671880269456</v>
       </c>
       <c r="D19" t="n">
-        <v>6.758940244657591</v>
+        <v>7.755689053825292</v>
       </c>
       <c r="E19" t="n">
-        <v>21.32948989237437</v>
+        <v>21.77433941212269</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.051332375592583</v>
+        <v>1.796843735697725</v>
       </c>
       <c r="C20" t="n">
-        <v>14.61291206115503</v>
+        <v>14.23487047268071</v>
       </c>
       <c r="D20" t="n">
-        <v>7.286001317159533</v>
+        <v>8.287374158014238</v>
       </c>
       <c r="E20" t="n">
-        <v>23.95024575390715</v>
+        <v>24.31908836639267</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.225505841734251</v>
+        <v>1.07192123088188</v>
       </c>
       <c r="C21" t="n">
-        <v>10.7098268007662</v>
+        <v>10.47888047081918</v>
       </c>
       <c r="D21" t="n">
-        <v>6.104841019226111</v>
+        <v>6.965156349934634</v>
       </c>
       <c r="E21" t="n">
-        <v>18.04017366172656</v>
+        <v>18.5159580516357</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_61_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_61_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.25067435315222</v>
+        <v>1.251685553287595</v>
       </c>
       <c r="C3" t="n">
-        <v>4.646049233825782</v>
+        <v>4.635289278987237</v>
       </c>
       <c r="D3" t="n">
-        <v>6.101144833054261</v>
+        <v>6.032697383114175</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99786842003226</v>
+        <v>11.91967221538901</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.370616014667294</v>
+        <v>1.375312387182994</v>
       </c>
       <c r="C4" t="n">
-        <v>5.170187911114808</v>
+        <v>5.168540193868463</v>
       </c>
       <c r="D4" t="n">
-        <v>6.502601069062296</v>
+        <v>6.363528269980628</v>
       </c>
       <c r="E4" t="n">
-        <v>13.0434049948444</v>
+        <v>12.90738085103209</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.534896116959291</v>
+        <v>1.560138751145023</v>
       </c>
       <c r="C5" t="n">
-        <v>5.825039757796503</v>
+        <v>5.833143063093925</v>
       </c>
       <c r="D5" t="n">
-        <v>6.832103668825276</v>
+        <v>6.6897000143457</v>
       </c>
       <c r="E5" t="n">
-        <v>14.19203954358107</v>
+        <v>14.08298182858465</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.724327004521076</v>
+        <v>1.776631518239721</v>
       </c>
       <c r="C6" t="n">
-        <v>6.626549496655651</v>
+        <v>6.629620732502805</v>
       </c>
       <c r="D6" t="n">
-        <v>7.352057000004535</v>
+        <v>7.006350975547939</v>
       </c>
       <c r="E6" t="n">
-        <v>15.70293350118126</v>
+        <v>15.41260322629046</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.933084855301881</v>
+        <v>2.012313032138653</v>
       </c>
       <c r="C7" t="n">
-        <v>7.570774390771291</v>
+        <v>7.536664206303349</v>
       </c>
       <c r="D7" t="n">
-        <v>7.764617743177852</v>
+        <v>7.324366454212445</v>
       </c>
       <c r="E7" t="n">
-        <v>17.26847698925102</v>
+        <v>16.87334369265445</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.161418265847751</v>
+        <v>1.245928040414225</v>
       </c>
       <c r="C8" t="n">
-        <v>5.219426062044588</v>
+        <v>5.069158680189044</v>
       </c>
       <c r="D8" t="n">
-        <v>5.992760363974981</v>
+        <v>5.67832679187438</v>
       </c>
       <c r="E8" t="n">
-        <v>12.37360469186732</v>
+        <v>11.99341351247765</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.449656636749821</v>
+        <v>1.565216114881836</v>
       </c>
       <c r="C9" t="n">
-        <v>6.389186370458434</v>
+        <v>6.097325931256162</v>
       </c>
       <c r="D9" t="n">
-        <v>6.515556245053477</v>
+        <v>6.17637069761209</v>
       </c>
       <c r="E9" t="n">
-        <v>14.35439925226173</v>
+        <v>13.83891274375009</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.748087354983464</v>
+        <v>1.923246468198132</v>
       </c>
       <c r="C10" t="n">
-        <v>7.693089312368494</v>
+        <v>7.265957581236543</v>
       </c>
       <c r="D10" t="n">
-        <v>7.085539493977075</v>
+        <v>6.644719956953667</v>
       </c>
       <c r="E10" t="n">
-        <v>16.52671616132903</v>
+        <v>15.83392400638834</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.056822697350973</v>
+        <v>2.293744505437957</v>
       </c>
       <c r="C11" t="n">
-        <v>9.105670047672584</v>
+        <v>8.540681004848521</v>
       </c>
       <c r="D11" t="n">
-        <v>7.755072904863267</v>
+        <v>7.278087417376055</v>
       </c>
       <c r="E11" t="n">
-        <v>18.91756564988682</v>
+        <v>18.11251292766253</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.355956558952342</v>
+        <v>2.669688043210878</v>
       </c>
       <c r="C12" t="n">
-        <v>10.59269388132084</v>
+        <v>9.875953228361764</v>
       </c>
       <c r="D12" t="n">
-        <v>8.348205553743034</v>
+        <v>7.811867995257673</v>
       </c>
       <c r="E12" t="n">
-        <v>21.29685599401622</v>
+        <v>20.35750926683032</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.647465084340884</v>
+        <v>3.043973321873712</v>
       </c>
       <c r="C13" t="n">
-        <v>12.14280747161502</v>
+        <v>11.25319818897914</v>
       </c>
       <c r="D13" t="n">
-        <v>9.007795093064074</v>
+        <v>8.361198842889333</v>
       </c>
       <c r="E13" t="n">
-        <v>23.79806764901998</v>
+        <v>22.65837035374219</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.526971109277319</v>
+        <v>1.747805437870597</v>
       </c>
       <c r="C14" t="n">
-        <v>8.56455098735424</v>
+        <v>7.999496278697945</v>
       </c>
       <c r="D14" t="n">
-        <v>6.810933603074502</v>
+        <v>6.374694010692432</v>
       </c>
       <c r="E14" t="n">
-        <v>16.90245569970606</v>
+        <v>16.12199572726097</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.552977605962817</v>
+        <v>1.815968180976453</v>
       </c>
       <c r="C15" t="n">
-        <v>9.232316140828836</v>
+        <v>8.481573671391299</v>
       </c>
       <c r="D15" t="n">
-        <v>6.911994711749669</v>
+        <v>6.438360349312838</v>
       </c>
       <c r="E15" t="n">
-        <v>17.69728845854132</v>
+        <v>16.73590220168059</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.786447027509751</v>
+        <v>2.128851174319911</v>
       </c>
       <c r="C16" t="n">
-        <v>10.87238458563539</v>
+        <v>9.909407897493775</v>
       </c>
       <c r="D16" t="n">
-        <v>7.536356799219512</v>
+        <v>6.96860228437654</v>
       </c>
       <c r="E16" t="n">
-        <v>20.19518841236465</v>
+        <v>19.00686135619023</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.422306986527567</v>
+        <v>1.725156518333623</v>
       </c>
       <c r="C17" t="n">
-        <v>9.990902774423304</v>
+        <v>9.019669588088977</v>
       </c>
       <c r="D17" t="n">
-        <v>7.077448652346384</v>
+        <v>6.525235203661638</v>
       </c>
       <c r="E17" t="n">
-        <v>18.49065841329725</v>
+        <v>17.27006131008424</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.614346654955285</v>
+        <v>1.991514487972825</v>
       </c>
       <c r="C18" t="n">
-        <v>11.62786889648444</v>
+        <v>10.44479419052773</v>
       </c>
       <c r="D18" t="n">
-        <v>7.597009172387881</v>
+        <v>7.018975759081443</v>
       </c>
       <c r="E18" t="n">
-        <v>20.8392247238276</v>
+        <v>19.455284437582</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.611931555602838</v>
+        <v>2.023578367993526</v>
       </c>
       <c r="C19" t="n">
-        <v>12.40671880269456</v>
+        <v>11.08701426873783</v>
       </c>
       <c r="D19" t="n">
-        <v>7.755689053825292</v>
+        <v>7.151011007825597</v>
       </c>
       <c r="E19" t="n">
-        <v>21.77433941212269</v>
+        <v>20.26160364455695</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.796843735697725</v>
+        <v>2.276270409589612</v>
       </c>
       <c r="C20" t="n">
-        <v>14.23487047268071</v>
+        <v>12.74231943791429</v>
       </c>
       <c r="D20" t="n">
-        <v>8.287374158014238</v>
+        <v>7.709154212643994</v>
       </c>
       <c r="E20" t="n">
-        <v>24.31908836639267</v>
+        <v>22.72774406014789</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.07192123088188</v>
+        <v>1.364806023489831</v>
       </c>
       <c r="C21" t="n">
-        <v>10.47888047081918</v>
+        <v>9.410542619057802</v>
       </c>
       <c r="D21" t="n">
-        <v>6.965156349934634</v>
+        <v>6.473074948135004</v>
       </c>
       <c r="E21" t="n">
-        <v>18.5159580516357</v>
+        <v>17.24842359068264</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_61_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_61_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.251685553287595</v>
+        <v>2.579610337131321</v>
       </c>
       <c r="C3" t="n">
-        <v>4.635289278987237</v>
+        <v>7.640370137840968</v>
       </c>
       <c r="D3" t="n">
-        <v>6.032697383114175</v>
+        <v>8.195470560477116</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91967221538901</v>
+        <v>18.4154510354494</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.375312387182994</v>
+        <v>1.050646083264753</v>
       </c>
       <c r="C4" t="n">
-        <v>5.168540193868463</v>
+        <v>4.385994983315094</v>
       </c>
       <c r="D4" t="n">
-        <v>6.363528269980628</v>
+        <v>5.820547128537716</v>
       </c>
       <c r="E4" t="n">
-        <v>12.90738085103209</v>
+        <v>11.25718819511756</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.560138751145023</v>
+        <v>1.128519010273172</v>
       </c>
       <c r="C5" t="n">
-        <v>5.833143063093925</v>
+        <v>4.963641449036528</v>
       </c>
       <c r="D5" t="n">
-        <v>6.6897000143457</v>
+        <v>6.119484077836214</v>
       </c>
       <c r="E5" t="n">
-        <v>14.08298182858465</v>
+        <v>12.21164453714591</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.776631518239721</v>
+        <v>1.219653218461747</v>
       </c>
       <c r="C6" t="n">
-        <v>6.629620732502805</v>
+        <v>5.725090540159077</v>
       </c>
       <c r="D6" t="n">
-        <v>7.006350975547939</v>
+        <v>6.451724973567451</v>
       </c>
       <c r="E6" t="n">
-        <v>15.41260322629046</v>
+        <v>13.39646873218827</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.012313032138653</v>
+        <v>1.316422371656551</v>
       </c>
       <c r="C7" t="n">
-        <v>7.536664206303349</v>
+        <v>6.637577008482022</v>
       </c>
       <c r="D7" t="n">
-        <v>7.324366454212445</v>
+        <v>6.843206609190321</v>
       </c>
       <c r="E7" t="n">
-        <v>16.87334369265445</v>
+        <v>14.79720598932889</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.245928040414225</v>
+        <v>1.419048537259594</v>
       </c>
       <c r="C8" t="n">
-        <v>5.069158680189044</v>
+        <v>7.677657248744766</v>
       </c>
       <c r="D8" t="n">
-        <v>5.67832679187438</v>
+        <v>7.2142996118574</v>
       </c>
       <c r="E8" t="n">
-        <v>11.99341351247765</v>
+        <v>16.31100539786176</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.565216114881836</v>
+        <v>1.525773568213517</v>
       </c>
       <c r="C9" t="n">
-        <v>6.097325931256162</v>
+        <v>8.833460483274237</v>
       </c>
       <c r="D9" t="n">
-        <v>6.17637069761209</v>
+        <v>7.579629487639379</v>
       </c>
       <c r="E9" t="n">
-        <v>13.83891274375009</v>
+        <v>17.93886353912713</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.923246468198132</v>
+        <v>0.9713608135358791</v>
       </c>
       <c r="C10" t="n">
-        <v>7.265957581236543</v>
+        <v>6.513336421486167</v>
       </c>
       <c r="D10" t="n">
-        <v>6.644719956953667</v>
+        <v>5.959542358997583</v>
       </c>
       <c r="E10" t="n">
-        <v>15.83392400638834</v>
+        <v>13.44423959401963</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.293744505437957</v>
+        <v>0.8981322522761096</v>
       </c>
       <c r="C11" t="n">
-        <v>8.540681004848521</v>
+        <v>6.860256607735861</v>
       </c>
       <c r="D11" t="n">
-        <v>7.278087417376055</v>
+        <v>5.806055922915637</v>
       </c>
       <c r="E11" t="n">
-        <v>18.11251292766253</v>
+        <v>13.56444478292761</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.669688043210878</v>
+        <v>0.9551619764158068</v>
       </c>
       <c r="C12" t="n">
-        <v>9.875953228361764</v>
+        <v>8.071330758217684</v>
       </c>
       <c r="D12" t="n">
-        <v>7.811867995257673</v>
+        <v>6.224525881850839</v>
       </c>
       <c r="E12" t="n">
-        <v>20.35750926683032</v>
+        <v>15.25101861648433</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.043973321873712</v>
+        <v>0.7475321544446488</v>
       </c>
       <c r="C13" t="n">
-        <v>11.25319818897914</v>
+        <v>7.678592406610791</v>
       </c>
       <c r="D13" t="n">
-        <v>8.361198842889333</v>
+        <v>5.678634888381444</v>
       </c>
       <c r="E13" t="n">
-        <v>22.65837035374219</v>
+        <v>14.10475944943688</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.747805437870597</v>
+        <v>0.8030794395509333</v>
       </c>
       <c r="C14" t="n">
-        <v>7.999496278697945</v>
+        <v>9.004953190002315</v>
       </c>
       <c r="D14" t="n">
-        <v>6.374694010692432</v>
+        <v>6.045180211239033</v>
       </c>
       <c r="E14" t="n">
-        <v>16.12199572726097</v>
+        <v>15.85321284079228</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.815968180976453</v>
+        <v>0.7729496025075989</v>
       </c>
       <c r="C15" t="n">
-        <v>8.481573671391299</v>
+        <v>9.75333946494966</v>
       </c>
       <c r="D15" t="n">
-        <v>6.438360349312838</v>
+        <v>6.102337562580281</v>
       </c>
       <c r="E15" t="n">
-        <v>16.73590220168059</v>
+        <v>16.62862663003754</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.128851174319911</v>
+        <v>0.8511359896738148</v>
       </c>
       <c r="C16" t="n">
-        <v>9.909407897493775</v>
+        <v>11.44452751271634</v>
       </c>
       <c r="D16" t="n">
-        <v>6.96860228437654</v>
+        <v>6.494565405380968</v>
       </c>
       <c r="E16" t="n">
-        <v>19.00686135619023</v>
+        <v>18.79022890777113</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.725156518333623</v>
+        <v>0.5215240154499906</v>
       </c>
       <c r="C17" t="n">
-        <v>9.019669588088977</v>
+        <v>8.630769870005686</v>
       </c>
       <c r="D17" t="n">
-        <v>6.525235203661638</v>
+        <v>5.387851035860581</v>
       </c>
       <c r="E17" t="n">
-        <v>17.27006131008424</v>
+        <v>14.54014492131626</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.991514487972825</v>
+        <v>0.4108319617961628</v>
       </c>
       <c r="C18" t="n">
-        <v>10.44479419052773</v>
+        <v>7.672515388321503</v>
       </c>
       <c r="D18" t="n">
-        <v>7.018975759081443</v>
+        <v>4.893383987139632</v>
       </c>
       <c r="E18" t="n">
-        <v>19.455284437582</v>
+        <v>12.9767313372573</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.023578367993526</v>
+        <v>0.4886060149265952</v>
       </c>
       <c r="C19" t="n">
-        <v>11.08701426873783</v>
+        <v>9.51018019356181</v>
       </c>
       <c r="D19" t="n">
-        <v>7.151011007825597</v>
+        <v>5.407289640404668</v>
       </c>
       <c r="E19" t="n">
-        <v>20.26160364455695</v>
+        <v>15.40607584889307</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.276270409589612</v>
+        <v>0.5653001455823559</v>
       </c>
       <c r="C20" t="n">
-        <v>12.74231943791429</v>
+        <v>11.56911129638526</v>
       </c>
       <c r="D20" t="n">
-        <v>7.709154212643994</v>
+        <v>5.880462581420502</v>
       </c>
       <c r="E20" t="n">
-        <v>22.72774406014789</v>
+        <v>18.01487402338812</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.364806023489831</v>
+        <v>0.633315626532575</v>
       </c>
       <c r="C21" t="n">
-        <v>9.410542619057802</v>
+        <v>13.77803381346354</v>
       </c>
       <c r="D21" t="n">
-        <v>6.473074948135004</v>
+        <v>6.370403773224873</v>
       </c>
       <c r="E21" t="n">
-        <v>17.24842359068264</v>
+        <v>20.78175321322099</v>
       </c>
     </row>
   </sheetData>
